--- a/data/samsun/km_data.xlsx
+++ b/data/samsun/km_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -454,7 +454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:48</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -466,7 +466,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:48</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -486,7 +486,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:48</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -634,411 +634,10 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-09 08:44:56</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5011</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5017</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5018</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5019</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>4120</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>4121</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>4123</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>4125</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>4126</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:49</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>4127</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:50</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>4128</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-02-26 16:43:50</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
         <is>
           <t>bootstrap</t>
         </is>
